--- a/EBI_RV_v5_suppfile2_tableonly.xlsx
+++ b/EBI_RV_v5_suppfile2_tableonly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vjain\Documents\app.py\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A9AE1B69-95FD-40E3-B7F7-FC796A4D350E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FBE11B8-B3A2-4E07-BA6B-441EF87A4B60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{583704CB-8AC0-435A-98BB-7CF6B7C51031}"/>
   </bookViews>
@@ -936,16 +936,6 @@
         <family val="1"/>
       </rPr>
       <t>Chemoembolisation of mesothelioma</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.5"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t>Chronic Fatigure Syndrome - Inpatient/residential treatment</t>
     </r>
   </si>
   <si>
@@ -2278,6 +2268,9 @@
       <t>X-ray (Sinuses)</t>
     </r>
   </si>
+  <si>
+    <t>Chronic Fatigue Syndrome - Inpatient/residential treatment</t>
+  </si>
 </sst>
 </file>
 
@@ -2419,7 +2412,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2453,6 +2446,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7262,8 +7258,8 @@
       </c>
     </row>
     <row r="31" spans="1:49" ht="24" x14ac:dyDescent="0.35">
-      <c r="A31" s="5" t="s">
-        <v>83</v>
+      <c r="A31" s="12" t="s">
+        <v>216</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>50</v>
@@ -7412,7 +7408,7 @@
     </row>
     <row r="32" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B32" s="8" t="s">
         <v>52</v>
@@ -7561,7 +7557,7 @@
     </row>
     <row r="33" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A33" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>50</v>
@@ -7710,7 +7706,7 @@
     </row>
     <row r="34" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A34" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>51</v>
@@ -7859,7 +7855,7 @@
     </row>
     <row r="35" spans="1:49" ht="18" x14ac:dyDescent="0.35">
       <c r="A35" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>50</v>
@@ -8008,7 +8004,7 @@
     </row>
     <row r="36" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>51</v>
@@ -8157,7 +8153,7 @@
     </row>
     <row r="37" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A37" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>50</v>
@@ -8306,7 +8302,7 @@
     </row>
     <row r="38" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A38" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>50</v>
@@ -8455,7 +8451,7 @@
     </row>
     <row r="39" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A39" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>50</v>
@@ -8604,7 +8600,7 @@
     </row>
     <row r="40" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A40" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B40" s="8" t="s">
         <v>52</v>
@@ -8753,7 +8749,7 @@
     </row>
     <row r="41" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A41" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>51</v>
@@ -8902,7 +8898,7 @@
     </row>
     <row r="42" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A42" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B42" s="8" t="s">
         <v>52</v>
@@ -9051,7 +9047,7 @@
     </row>
     <row r="43" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A43" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>50</v>
@@ -9200,7 +9196,7 @@
     </row>
     <row r="44" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A44" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>51</v>
@@ -9349,7 +9345,7 @@
     </row>
     <row r="45" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A45" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B45" s="8" t="s">
         <v>52</v>
@@ -9498,7 +9494,7 @@
     </row>
     <row r="46" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A46" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>50</v>
@@ -9647,7 +9643,7 @@
     </row>
     <row r="47" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A47" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B47" s="8" t="s">
         <v>52</v>
@@ -9796,7 +9792,7 @@
     </row>
     <row r="48" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A48" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>50</v>
@@ -9945,7 +9941,7 @@
     </row>
     <row r="49" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A49" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>50</v>
@@ -10094,7 +10090,7 @@
     </row>
     <row r="50" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A50" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>50</v>
@@ -10243,7 +10239,7 @@
     </row>
     <row r="51" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A51" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B51" s="8" t="s">
         <v>52</v>
@@ -10392,7 +10388,7 @@
     </row>
     <row r="52" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A52" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B52" s="7" t="s">
         <v>51</v>
@@ -10541,7 +10537,7 @@
     </row>
     <row r="53" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A53" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>50</v>
@@ -10690,7 +10686,7 @@
     </row>
     <row r="54" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A54" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>50</v>
@@ -10839,7 +10835,7 @@
     </row>
     <row r="55" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A55" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B55" s="8" t="s">
         <v>52</v>
@@ -10988,7 +10984,7 @@
     </row>
     <row r="56" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A56" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B56" s="8" t="s">
         <v>52</v>
@@ -11137,7 +11133,7 @@
     </row>
     <row r="57" spans="1:49" ht="18" x14ac:dyDescent="0.35">
       <c r="A57" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>50</v>
@@ -11286,7 +11282,7 @@
     </row>
     <row r="58" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A58" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B58" s="8" t="s">
         <v>52</v>
@@ -11435,7 +11431,7 @@
     </row>
     <row r="59" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A59" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B59" s="8" t="s">
         <v>52</v>
@@ -11584,7 +11580,7 @@
     </row>
     <row r="60" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A60" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>50</v>
@@ -11733,7 +11729,7 @@
     </row>
     <row r="61" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A61" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B61" s="8" t="s">
         <v>52</v>
@@ -11882,7 +11878,7 @@
     </row>
     <row r="62" spans="1:49" ht="18" x14ac:dyDescent="0.35">
       <c r="A62" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>51</v>
@@ -12031,7 +12027,7 @@
     </row>
     <row r="63" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A63" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>50</v>
@@ -12180,7 +12176,7 @@
     </row>
     <row r="64" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A64" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>51</v>
@@ -12329,7 +12325,7 @@
     </row>
     <row r="65" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A65" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>50</v>
@@ -12478,7 +12474,7 @@
     </row>
     <row r="66" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A66" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>50</v>
@@ -12627,7 +12623,7 @@
     </row>
     <row r="67" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A67" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>50</v>
@@ -12776,7 +12772,7 @@
     </row>
     <row r="68" spans="1:49" ht="18" x14ac:dyDescent="0.35">
       <c r="A68" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>50</v>
@@ -12925,7 +12921,7 @@
     </row>
     <row r="69" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A69" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B69" s="8" t="s">
         <v>52</v>
@@ -13074,7 +13070,7 @@
     </row>
     <row r="70" spans="1:49" ht="18" x14ac:dyDescent="0.35">
       <c r="A70" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B70" s="7" t="s">
         <v>51</v>
@@ -13223,7 +13219,7 @@
     </row>
     <row r="71" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A71" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B71" s="7" t="s">
         <v>51</v>
@@ -13372,7 +13368,7 @@
     </row>
     <row r="72" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A72" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>50</v>
@@ -13521,7 +13517,7 @@
     </row>
     <row r="73" spans="1:49" ht="18" x14ac:dyDescent="0.35">
       <c r="A73" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>50</v>
@@ -13670,7 +13666,7 @@
     </row>
     <row r="74" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A74" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B74" s="8" t="s">
         <v>52</v>
@@ -13819,7 +13815,7 @@
     </row>
     <row r="75" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A75" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>50</v>
@@ -13968,7 +13964,7 @@
     </row>
     <row r="76" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A76" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B76" s="8" t="s">
         <v>52</v>
@@ -14117,7 +14113,7 @@
     </row>
     <row r="77" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A77" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>50</v>
@@ -14266,7 +14262,7 @@
     </row>
     <row r="78" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A78" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>50</v>
@@ -14415,7 +14411,7 @@
     </row>
     <row r="79" spans="1:49" ht="24" x14ac:dyDescent="0.35">
       <c r="A79" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B79" s="8" t="s">
         <v>52</v>
@@ -14564,7 +14560,7 @@
     </row>
     <row r="80" spans="1:49" ht="24" x14ac:dyDescent="0.35">
       <c r="A80" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>50</v>
@@ -14713,7 +14709,7 @@
     </row>
     <row r="81" spans="1:49" ht="18" x14ac:dyDescent="0.35">
       <c r="A81" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>50</v>
@@ -14862,7 +14858,7 @@
     </row>
     <row r="82" spans="1:49" ht="18" x14ac:dyDescent="0.35">
       <c r="A82" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>50</v>
@@ -15011,7 +15007,7 @@
     </row>
     <row r="83" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A83" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B83" s="8" t="s">
         <v>52</v>
@@ -15160,7 +15156,7 @@
     </row>
     <row r="84" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A84" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B84" s="7" t="s">
         <v>51</v>
@@ -15309,7 +15305,7 @@
     </row>
     <row r="85" spans="1:49" ht="18" x14ac:dyDescent="0.35">
       <c r="A85" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B85" s="6" t="s">
         <v>50</v>
@@ -15458,7 +15454,7 @@
     </row>
     <row r="86" spans="1:49" ht="18" x14ac:dyDescent="0.35">
       <c r="A86" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B86" s="6" t="s">
         <v>50</v>
@@ -15607,7 +15603,7 @@
     </row>
     <row r="87" spans="1:49" ht="18" x14ac:dyDescent="0.35">
       <c r="A87" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B87" s="8" t="s">
         <v>52</v>
@@ -15756,7 +15752,7 @@
     </row>
     <row r="88" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A88" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B88" s="6" t="s">
         <v>50</v>
@@ -15905,7 +15901,7 @@
     </row>
     <row r="89" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A89" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B89" s="8" t="s">
         <v>52</v>
@@ -16054,7 +16050,7 @@
     </row>
     <row r="90" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A90" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B90" s="6" t="s">
         <v>50</v>
@@ -16203,7 +16199,7 @@
     </row>
     <row r="91" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A91" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B91" s="6" t="s">
         <v>50</v>
@@ -16352,7 +16348,7 @@
     </row>
     <row r="92" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A92" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>50</v>
@@ -16501,7 +16497,7 @@
     </row>
     <row r="93" spans="1:49" ht="24" x14ac:dyDescent="0.35">
       <c r="A93" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B93" s="6" t="s">
         <v>50</v>
@@ -16650,7 +16646,7 @@
     </row>
     <row r="94" spans="1:49" ht="18" x14ac:dyDescent="0.35">
       <c r="A94" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>50</v>
@@ -16799,7 +16795,7 @@
     </row>
     <row r="95" spans="1:49" ht="24" x14ac:dyDescent="0.35">
       <c r="A95" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B95" s="6" t="s">
         <v>50</v>
@@ -16948,7 +16944,7 @@
     </row>
     <row r="96" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A96" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B96" s="7" t="s">
         <v>51</v>
@@ -17097,7 +17093,7 @@
     </row>
     <row r="97" spans="1:49" ht="18" x14ac:dyDescent="0.35">
       <c r="A97" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B97" s="6" t="s">
         <v>50</v>
@@ -17246,7 +17242,7 @@
     </row>
     <row r="98" spans="1:49" ht="30" x14ac:dyDescent="0.35">
       <c r="A98" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B98" s="8" t="s">
         <v>52</v>
@@ -17395,7 +17391,7 @@
     </row>
     <row r="99" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A99" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B99" s="6" t="s">
         <v>50</v>
@@ -17544,7 +17540,7 @@
     </row>
     <row r="100" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A100" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B100" s="6" t="s">
         <v>50</v>
@@ -17693,7 +17689,7 @@
     </row>
     <row r="101" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A101" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B101" s="8" t="s">
         <v>52</v>
@@ -17842,7 +17838,7 @@
     </row>
     <row r="102" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A102" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B102" s="8" t="s">
         <v>52</v>
@@ -17991,7 +17987,7 @@
     </row>
     <row r="103" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A103" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B103" s="6" t="s">
         <v>50</v>
@@ -18140,7 +18136,7 @@
     </row>
     <row r="104" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A104" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B104" s="6" t="s">
         <v>50</v>
@@ -18289,7 +18285,7 @@
     </row>
     <row r="105" spans="1:49" ht="18" x14ac:dyDescent="0.35">
       <c r="A105" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B105" s="6" t="s">
         <v>50</v>
@@ -18438,7 +18434,7 @@
     </row>
     <row r="106" spans="1:49" ht="18" x14ac:dyDescent="0.35">
       <c r="A106" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B106" s="6" t="s">
         <v>50</v>
@@ -18587,7 +18583,7 @@
     </row>
     <row r="107" spans="1:49" ht="36" x14ac:dyDescent="0.35">
       <c r="A107" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B107" s="6" t="s">
         <v>50</v>
@@ -18736,7 +18732,7 @@
     </row>
     <row r="108" spans="1:49" ht="18" x14ac:dyDescent="0.35">
       <c r="A108" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B108" s="8" t="s">
         <v>52</v>
@@ -18885,7 +18881,7 @@
     </row>
     <row r="109" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A109" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B109" s="6" t="s">
         <v>50</v>
@@ -19034,7 +19030,7 @@
     </row>
     <row r="110" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A110" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B110" s="8" t="s">
         <v>52</v>
@@ -19183,7 +19179,7 @@
     </row>
     <row r="111" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A111" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B111" s="6" t="s">
         <v>50</v>
@@ -19332,7 +19328,7 @@
     </row>
     <row r="112" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A112" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B112" s="6" t="s">
         <v>50</v>
@@ -19481,7 +19477,7 @@
     </row>
     <row r="113" spans="1:49" ht="24" x14ac:dyDescent="0.35">
       <c r="A113" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B113" s="6" t="s">
         <v>50</v>
@@ -19630,7 +19626,7 @@
     </row>
     <row r="114" spans="1:49" ht="24" x14ac:dyDescent="0.35">
       <c r="A114" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B114" s="6" t="s">
         <v>50</v>
@@ -19779,7 +19775,7 @@
     </row>
     <row r="115" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A115" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B115" s="6" t="s">
         <v>50</v>
@@ -19928,7 +19924,7 @@
     </row>
     <row r="116" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A116" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B116" s="6" t="s">
         <v>50</v>
@@ -20077,7 +20073,7 @@
     </row>
     <row r="117" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A117" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B117" s="8" t="s">
         <v>52</v>
@@ -20226,7 +20222,7 @@
     </row>
     <row r="118" spans="1:49" ht="18" x14ac:dyDescent="0.35">
       <c r="A118" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B118" s="6" t="s">
         <v>50</v>
@@ -20375,7 +20371,7 @@
     </row>
     <row r="119" spans="1:49" ht="30" x14ac:dyDescent="0.35">
       <c r="A119" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B119" s="8" t="s">
         <v>52</v>
@@ -20524,7 +20520,7 @@
     </row>
     <row r="120" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A120" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B120" s="6" t="s">
         <v>50</v>
@@ -20673,7 +20669,7 @@
     </row>
     <row r="121" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A121" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B121" s="6" t="s">
         <v>50</v>
@@ -20822,7 +20818,7 @@
     </row>
     <row r="122" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A122" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B122" s="8" t="s">
         <v>52</v>
@@ -20971,7 +20967,7 @@
     </row>
     <row r="123" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A123" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>51</v>
@@ -21120,7 +21116,7 @@
     </row>
     <row r="124" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A124" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B124" s="6" t="s">
         <v>50</v>
@@ -21269,7 +21265,7 @@
     </row>
     <row r="125" spans="1:49" ht="18" x14ac:dyDescent="0.35">
       <c r="A125" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B125" s="7" t="s">
         <v>51</v>
@@ -21418,7 +21414,7 @@
     </row>
     <row r="126" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A126" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B126" s="8" t="s">
         <v>52</v>
@@ -21567,7 +21563,7 @@
     </row>
     <row r="127" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A127" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B127" s="6" t="s">
         <v>50</v>
@@ -21716,7 +21712,7 @@
     </row>
     <row r="128" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A128" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B128" s="8" t="s">
         <v>52</v>
@@ -21865,7 +21861,7 @@
     </row>
     <row r="129" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A129" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B129" s="8" t="s">
         <v>52</v>
@@ -22014,7 +22010,7 @@
     </row>
     <row r="130" spans="1:49" ht="30" x14ac:dyDescent="0.35">
       <c r="A130" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B130" s="8" t="s">
         <v>52</v>
@@ -22163,7 +22159,7 @@
     </row>
     <row r="131" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A131" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B131" s="8" t="s">
         <v>52</v>
@@ -22312,7 +22308,7 @@
     </row>
     <row r="132" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A132" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B132" s="8" t="s">
         <v>52</v>
@@ -22461,7 +22457,7 @@
     </row>
     <row r="133" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A133" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B133" s="8" t="s">
         <v>52</v>
@@ -22610,7 +22606,7 @@
     </row>
     <row r="134" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A134" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B134" s="8" t="s">
         <v>52</v>
@@ -22759,7 +22755,7 @@
     </row>
     <row r="135" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A135" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B135" s="6" t="s">
         <v>50</v>
@@ -22908,7 +22904,7 @@
     </row>
     <row r="136" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A136" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B136" s="6" t="s">
         <v>50</v>
@@ -23057,7 +23053,7 @@
     </row>
     <row r="137" spans="1:49" ht="18" x14ac:dyDescent="0.35">
       <c r="A137" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B137" s="8" t="s">
         <v>52</v>
@@ -23206,7 +23202,7 @@
     </row>
     <row r="138" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A138" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B138" s="6" t="s">
         <v>50</v>
@@ -23355,7 +23351,7 @@
     </row>
     <row r="139" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A139" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B139" s="6" t="s">
         <v>50</v>
@@ -23504,7 +23500,7 @@
     </row>
     <row r="140" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A140" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B140" s="6" t="s">
         <v>50</v>
@@ -23653,7 +23649,7 @@
     </row>
     <row r="141" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A141" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B141" s="6" t="s">
         <v>50</v>
@@ -23802,7 +23798,7 @@
     </row>
     <row r="142" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A142" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B142" s="6" t="s">
         <v>50</v>
@@ -23951,7 +23947,7 @@
     </row>
     <row r="143" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A143" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B143" s="8" t="s">
         <v>52</v>
@@ -24100,7 +24096,7 @@
     </row>
     <row r="144" spans="1:49" ht="18" x14ac:dyDescent="0.35">
       <c r="A144" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B144" s="8" t="s">
         <v>52</v>
@@ -24249,7 +24245,7 @@
     </row>
     <row r="145" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A145" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B145" s="8" t="s">
         <v>52</v>
@@ -24398,7 +24394,7 @@
     </row>
     <row r="146" spans="1:49" ht="18" x14ac:dyDescent="0.35">
       <c r="A146" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B146" s="6" t="s">
         <v>50</v>
@@ -24547,7 +24543,7 @@
     </row>
     <row r="147" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A147" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B147" s="7" t="s">
         <v>51</v>
@@ -24696,7 +24692,7 @@
     </row>
     <row r="148" spans="1:49" ht="18" x14ac:dyDescent="0.35">
       <c r="A148" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B148" s="8" t="s">
         <v>52</v>
@@ -24845,7 +24841,7 @@
     </row>
     <row r="149" spans="1:49" ht="18" x14ac:dyDescent="0.35">
       <c r="A149" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B149" s="7" t="s">
         <v>51</v>
@@ -24994,7 +24990,7 @@
     </row>
     <row r="150" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A150" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B150" s="7" t="s">
         <v>51</v>
@@ -25143,7 +25139,7 @@
     </row>
     <row r="151" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A151" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B151" s="6" t="s">
         <v>50</v>
@@ -25292,7 +25288,7 @@
     </row>
     <row r="152" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A152" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B152" s="6" t="s">
         <v>50</v>
@@ -25441,7 +25437,7 @@
     </row>
     <row r="153" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A153" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B153" s="8" t="s">
         <v>52</v>
@@ -25590,7 +25586,7 @@
     </row>
     <row r="154" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A154" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B154" s="7" t="s">
         <v>51</v>
@@ -25739,7 +25735,7 @@
     </row>
     <row r="155" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A155" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B155" s="6" t="s">
         <v>50</v>
@@ -25888,7 +25884,7 @@
     </row>
     <row r="156" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A156" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B156" s="6" t="s">
         <v>50</v>
@@ -26037,7 +26033,7 @@
     </row>
     <row r="157" spans="1:49" ht="30" x14ac:dyDescent="0.35">
       <c r="A157" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B157" s="6" t="s">
         <v>50</v>
@@ -26186,7 +26182,7 @@
     </row>
     <row r="158" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A158" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B158" s="6" t="s">
         <v>50</v>
@@ -26335,7 +26331,7 @@
     </row>
     <row r="159" spans="1:49" ht="30" x14ac:dyDescent="0.35">
       <c r="A159" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B159" s="11" t="s">
         <v>50</v>
@@ -26484,7 +26480,7 @@
     </row>
     <row r="160" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A160" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B160" s="6" t="s">
         <v>50</v>
@@ -26633,7 +26629,7 @@
     </row>
     <row r="161" spans="1:49" ht="24" x14ac:dyDescent="0.35">
       <c r="A161" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B161" s="6" t="s">
         <v>50</v>
@@ -26782,7 +26778,7 @@
     </row>
     <row r="162" spans="1:49" ht="24" x14ac:dyDescent="0.35">
       <c r="A162" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B162" s="8" t="s">
         <v>52</v>
@@ -26931,7 +26927,7 @@
     </row>
     <row r="163" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A163" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B163" s="6" t="s">
         <v>50</v>
@@ -27080,7 +27076,7 @@
     </row>
     <row r="164" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A164" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B164" s="6" t="s">
         <v>50</v>
